--- a/output/casestudy_20260905.xlsx
+++ b/output/casestudy_20260905.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>23.8566034999676</v>
+        <v>23.08603410003707</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24.60180959990248</v>
+        <v>23.34618999995291</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16.27597149997018</v>
+        <v>15.41464790003374</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25.45594930020161</v>
+        <v>23.95794610003941</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27.38536990014836</v>
+        <v>25.86469670012593</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>21.25082230009139</v>
+        <v>19.85025559994392</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>35.0172335000243</v>
+        <v>33.37941069994122</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.9 초</t>
+          <t>23.1 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.6 초</t>
+          <t>23.3 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16.3 초</t>
+          <t>15.4 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5 초</t>
+          <t>24.0 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.4 초</t>
+          <t>25.9 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21.3 초</t>
+          <t>19.9 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>35.0 초</t>
+          <t>33.4 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>180.3 초</t>
+          <t>170.8 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260905.xlsx
+++ b/output/casestudy_20260905.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>23.08603410003707</v>
+        <v>27.51000989996828</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23.34618999995291</v>
+        <v>25.11163379997015</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15.41464790003374</v>
+        <v>16.64305860013701</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>23.95794610003941</v>
+        <v>25.68100060010329</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>25.86469670012593</v>
+        <v>28.99738419987261</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>19.85025559994392</v>
+        <v>25.5898589999415</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>33.37941069994122</v>
+        <v>36.68464490002953</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.1 초</t>
+          <t>27.5 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>23.3 초</t>
+          <t>25.1 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>15.4 초</t>
+          <t>16.6 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.0 초</t>
+          <t>25.7 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.9 초</t>
+          <t>29.0 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19.9 초</t>
+          <t>25.6 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>33.4 초</t>
+          <t>36.7 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>170.8 초</t>
+          <t>196.4 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260905.xlsx
+++ b/output/casestudy_20260905.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>27.51000989996828</v>
+        <v>24.23804440000094</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>25.11163379997015</v>
+        <v>24.70467959996313</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16.64305860013701</v>
+        <v>16.47690790006891</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25.68100060010329</v>
+        <v>25.67450920003466</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>28.99738419987261</v>
+        <v>27.59350000019185</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>25.5898589999415</v>
+        <v>21.18972550006583</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>36.68464490002953</v>
+        <v>35.55740219983272</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27.5 초</t>
+          <t>24.2 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25.1 초</t>
+          <t>24.7 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16.6 초</t>
+          <t>16.5 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29.0 초</t>
+          <t>27.6 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25.6 초</t>
+          <t>21.2 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>36.7 초</t>
+          <t>35.6 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>196.4 초</t>
+          <t>182.0 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260905.xlsx
+++ b/output/casestudy_20260905.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>24.23804440000094</v>
+        <v>24.33998379996046</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24.70467959996313</v>
+        <v>24.72081740014255</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16.47690790006891</v>
+        <v>15.97628810000606</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25.67450920003466</v>
+        <v>25.19582400005311</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27.59350000019185</v>
+        <v>27.33501809998415</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>21.18972550006583</v>
+        <v>21.24736799998209</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>35.55740219983272</v>
+        <v>35.88598600006662</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.2 초</t>
+          <t>24.3 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16.5 초</t>
+          <t>16.0 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.7 초</t>
+          <t>25.2 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.6 초</t>
+          <t>27.3 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>35.6 초</t>
+          <t>35.9 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>182.0 초</t>
+          <t>181.1 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260905.xlsx
+++ b/output/casestudy_20260905.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>24.33998379996046</v>
+        <v>23.65601639985107</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24.72081740014255</v>
+        <v>24.17003100016154</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15.97628810000606</v>
+        <v>16.03790869982913</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25.19582400005311</v>
+        <v>25.34048480005004</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27.33501809998415</v>
+        <v>27.12770659988746</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>21.24736799998209</v>
+        <v>20.88912569987588</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>35.88598600006662</v>
+        <v>34.34406580007635</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.3 초</t>
+          <t>23.7 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.7 초</t>
+          <t>24.2 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.2 초</t>
+          <t>25.3 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.3 초</t>
+          <t>27.1 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21.2 초</t>
+          <t>20.9 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>35.9 초</t>
+          <t>34.3 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>181.1 초</t>
+          <t>177.9 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260905.xlsx
+++ b/output/casestudy_20260905.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>23.65601639985107</v>
+        <v>22.87933579995297</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>24.17003100016154</v>
+        <v>23.3227047000546</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>16.03790869982913</v>
+        <v>15.05754390009679</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>25.34048480005004</v>
+        <v>23.73889599996619</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27.12770659988746</v>
+        <v>25.64885320002213</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>20.88912569987588</v>
+        <v>19.78384850011207</v>
       </c>
     </row>
     <row r="8">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>34.34406580007635</v>
+        <v>33.11343610007316</v>
       </c>
     </row>
   </sheetData>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.7 초</t>
+          <t>22.9 초</t>
         </is>
       </c>
     </row>
@@ -9287,7 +9287,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.2 초</t>
+          <t>23.3 초</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16.0 초</t>
+          <t>15.1 초</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.3 초</t>
+          <t>23.7 초</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>27.1 초</t>
+          <t>25.6 초</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20.9 초</t>
+          <t>19.8 초</t>
         </is>
       </c>
     </row>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>34.3 초</t>
+          <t>33.1 초</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>177.9 초</t>
+          <t>169.4 초</t>
         </is>
       </c>
     </row>
